--- a/data/trans_camb/P19C09-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19C09-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,53</t>
+          <t>-3,32; 0,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,3</t>
+          <t>-1,97; 2,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,43; -0,42</t>
+          <t>-4,63; -0,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,07</t>
+          <t>-4,25; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; -0,37</t>
+          <t>-3,22; -0,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,6</t>
+          <t>-2,47; 0,56</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-75,5; 34,59</t>
+          <t>-77,14; 23,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,33; 126,72</t>
+          <t>-50,97; 113,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-80,34; -6,48</t>
+          <t>-79,12; 2,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-77,79; 5,32</t>
+          <t>-76,61; 4,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,63; -12,71</t>
+          <t>-70,72; -12,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,27; 22,48</t>
+          <t>-56,55; 21,82</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,24</t>
+          <t>-2,48; 0,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,76</t>
+          <t>-1,47; 1,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,35</t>
+          <t>-2,08; 1,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,9</t>
+          <t>-1,85; 1,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,42</t>
+          <t>-1,94; 0,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,28</t>
+          <t>-1,11; 1,3</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-77,63; 26,25</t>
+          <t>-73,59; 30,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,82; 111,44</t>
+          <t>-46,92; 109,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-50,95; 56,89</t>
+          <t>-49,03; 65,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,71; 81,68</t>
+          <t>-45,98; 70,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,51; 21,84</t>
+          <t>-51,92; 20,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,78; 57,28</t>
+          <t>-32,87; 56,24</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 0,53</t>
+          <t>-3,07; 0,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 2,4</t>
+          <t>-1,86; 2,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,82</t>
+          <t>-1,83; 2,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 0,09</t>
+          <t>-2,98; 0,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,72</t>
+          <t>-1,87; 0,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,68</t>
+          <t>-1,79; 0,63</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-82,28; 50,82</t>
+          <t>-79,35; 46,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,12; 162,86</t>
+          <t>-51,2; 147,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-53,43; 110,39</t>
+          <t>-53,93; 122,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-83,45; 11,68</t>
+          <t>-82,97; 27,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,16; 42,42</t>
+          <t>-57,88; 33,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,55; 40,29</t>
+          <t>-55,89; 36,21</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 1,45</t>
+          <t>-1,99; 1,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,07</t>
+          <t>-1,42; 1,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,61</t>
+          <t>-0,89; 2,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,4</t>
+          <t>-0,92; 2,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,49</t>
+          <t>-0,94; 1,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,67</t>
+          <t>-0,71; 1,73</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-57,61; 87,03</t>
+          <t>-58,93; 73,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,92; 110,93</t>
+          <t>-44,52; 109,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 139,98</t>
+          <t>-26,09; 140,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-32,6; 132,63</t>
+          <t>-28,92; 146,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,84; 77,04</t>
+          <t>-28,45; 71,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 78,63</t>
+          <t>-22,64; 87,67</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; -0,13</t>
+          <t>-1,75; -0,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,15</t>
+          <t>-0,71; 1,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,59</t>
+          <t>-1,27; 0,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,38</t>
+          <t>-1,37; 0,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; -0,04</t>
+          <t>-1,22; 0,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,46</t>
+          <t>-0,71; 0,53</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-57,34; -4,59</t>
+          <t>-56,35; -2,49</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 51,5</t>
+          <t>-23,79; 59,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-35,45; 22,96</t>
+          <t>-34,6; 20,59</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-38,09; 14,71</t>
+          <t>-39,36; 16,09</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,9; -0,88</t>
+          <t>-38,31; 0,43</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 17,95</t>
+          <t>-22,34; 21,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C09-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19C09-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,35</t>
+          <t>-3,19; 0,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 2,34</t>
+          <t>-2,14; 2,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,63; -0,33</t>
+          <t>-4,54; -0,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 0,0</t>
+          <t>-4,09; 0,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,22; -0,48</t>
+          <t>-3,23; -0,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,56</t>
+          <t>-2,48; 0,62</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-77,14; 23,47</t>
+          <t>-77,92; 38,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,97; 113,38</t>
+          <t>-50,18; 115,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-79,12; 2,69</t>
+          <t>-79,77; -11,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-76,61; 4,45</t>
+          <t>-74,29; 9,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-70,72; -12,05</t>
+          <t>-70,92; -11,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,55; 21,82</t>
+          <t>-55,8; 24,02</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,4</t>
+          <t>-2,64; 0,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,65</t>
+          <t>-1,49; 1,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,48</t>
+          <t>-2,12; 1,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,71</t>
+          <t>-1,94; 1,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,4</t>
+          <t>-1,8; 0,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,3</t>
+          <t>-1,05; 1,31</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-73,59; 30,38</t>
+          <t>-73,71; 26,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,92; 109,77</t>
+          <t>-43,27; 115,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,03; 65,23</t>
+          <t>-49,61; 60,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-45,98; 70,65</t>
+          <t>-44,92; 68,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,92; 20,07</t>
+          <t>-49,95; 23,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,87; 56,24</t>
+          <t>-31,22; 54,71</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,54</t>
+          <t>-3,15; 0,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 2,54</t>
+          <t>-1,78; 2,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,0</t>
+          <t>-2,01; 1,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 0,08</t>
+          <t>-3,28; 0,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,55</t>
+          <t>-2,01; 0,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,63</t>
+          <t>-1,97; 0,54</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-79,35; 46,04</t>
+          <t>-82,69; 34,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,2; 147,25</t>
+          <t>-52,11; 173,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-53,93; 122,67</t>
+          <t>-58,69; 104,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-82,97; 27,23</t>
+          <t>-84,23; 12,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-57,88; 33,42</t>
+          <t>-58,36; 37,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,89; 36,21</t>
+          <t>-57,64; 30,58</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 1,21</t>
+          <t>-1,9; 1,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,97</t>
+          <t>-1,44; 2,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,58</t>
+          <t>-0,92; 2,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 2,69</t>
+          <t>-1,03; 2,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,53</t>
+          <t>-0,92; 1,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,73</t>
+          <t>-0,61; 1,63</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-58,93; 73,32</t>
+          <t>-56,47; 82,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,52; 109,2</t>
+          <t>-41,85; 114,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 140,85</t>
+          <t>-28,57; 131,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,92; 146,04</t>
+          <t>-30,8; 125,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 71,57</t>
+          <t>-27,89; 69,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,64; 87,67</t>
+          <t>-20,19; 78,86</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,75; -0,09</t>
+          <t>-1,7; -0,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,29</t>
+          <t>-0,74; 1,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,54</t>
+          <t>-1,23; 0,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,42</t>
+          <t>-1,42; 0,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,01</t>
+          <t>-1,32; -0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,53</t>
+          <t>-0,81; 0,5</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-56,35; -2,49</t>
+          <t>-53,94; 0,68</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-23,79; 59,45</t>
+          <t>-24,78; 53,31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-34,6; 20,59</t>
+          <t>-33,47; 23,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 16,09</t>
+          <t>-38,51; 16,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 0,43</t>
+          <t>-39,49; -0,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-22,34; 21,09</t>
+          <t>-25,28; 19,99</t>
         </is>
       </c>
     </row>
